--- a/survey_templates/031_customer_experience_feedback_consent_form--survey_templates.xlsx
+++ b/survey_templates/031_customer_experience_feedback_consent_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_consent_form_1</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction and Consent</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Briefly introduce the purpose of this form and ask for consent to share feedback.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_2</t>
+          <t>demographics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Demographics</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide your basic demographics.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,18 +574,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>customer_experience_consent_form_3</t>
+          <t>experience_with_company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Consent</t>
+          <t>Experience with the Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,15 +597,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_4</t>
+          <t>satisfaction_with_product</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Satisfaction with the Product or Service</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please share your thoughts about our product or service.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,23 +619,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_5</t>
+          <t>quality_of_product</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
+          <t>Quality of the Product or Service</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,15 +647,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_6</t>
+          <t>feedback_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prophets and wizards</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or suggestions.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +669,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_7</t>
+          <t>experience_with_company_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Overall Experience with the Company</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please share your overall experience with the company.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +696,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_8</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Suggestions for Improvement</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please suggest ways we can improve our service.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +728,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_9</t>
+          <t>additional_comments_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional Comments 1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or suggestions.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,18 +755,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_10</t>
+          <t>feedback_willingness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
+          <t>Willingness to Provide Feedback</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,15 +778,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_11</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide your contact information for follow-up.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +805,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_12</t>
+          <t>additional_comments_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Additional Comments 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or suggestions.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,115 +827,115 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_13</t>
+          <t>satisfaction_with_company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
+          <t>Satisfaction with the Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_14</t>
+          <t>quality_of_support</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
+          <t>Quality of Support</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_15</t>
+          <t>timeliness_of_responses</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
+          <t>Timeliness of Responses</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_16</t>
+          <t>experience_with_communication</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
+          <t>Experience with Communication</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_17</t>
+          <t>experience_with_website</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
+          <t>Experience with the Website or Platform</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,177 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_18</t>
+          <t>final_comments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Final Comments</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please provide any final thoughts or comments.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_experience_feedback_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>customer_experience_feedback_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>customer_experience_feedback_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_experience_feedback_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>customer_experience_feedback_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>customer_experience_feedback_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>customer_experience_feedback_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Customer Experience Feedback</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +977,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,102 +1005,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_experience_consent_form_3_choices</t>
+          <t>experience_with_company_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>consent_to_receive_email_updates</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consent to receive email updates</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_experience_consent_form_3_choices</t>
+          <t>experience_with_company_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>consent_to_share_feedback_with_our_team</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consent to share feedback with our team</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_experience_consent_form_3_choices</t>
+          <t>experience_with_company_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prophets_and_wizards</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prophets and wizards</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_8_choices</t>
+          <t>experience_with_company_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_8_choices</t>
+          <t>quality_of_product_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_experience_feedback_form_8_choices</t>
+          <t>quality_of_product_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>quality_of_product_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>quality_of_product_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>satisfaction_with_company_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>satisfaction_with_company_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>satisfaction_with_company_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>satisfaction_with_company_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quality_of_support_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quality_of_support_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>quality_of_support_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>quality_of_support_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>timeliness_of_responses_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>timeliness_of_responses_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>timeliness_of_responses_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>timeliness_of_responses_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>experience_with_communication_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>experience_with_communication_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>experience_with_communication_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>experience_with_communication_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>experience_with_website_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>experience_with_website_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>experience_with_website_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>experience_with_website_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
